--- a/NY_State_Reports_2026-10-23/ESPN_Bet_Wynn_Interactive_Weekly_Report.xlsx
+++ b/NY_State_Reports_2026-10-23/ESPN_Bet_Wynn_Interactive_Weekly_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\MOBILE SPORTS WAGERING\11_Weekly Web Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF40F04-F3BC-4B05-888A-C7D840D7D4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DE5EAE-C3C1-406C-AF67-E630FA907972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA5EF8F-B63B-4D9E-966F-AB4A019BBE74}"/>
   </bookViews>
@@ -3033,9 +3033,14 @@
         <v>46313</v>
       </c>
       <c r="B42" s="20"/>
+      <c r="C42" s="21">
+        <v>7972264.8399999999</v>
+      </c>
       <c r="D42" s="37"/>
       <c r="E42" s="37"/>
-      <c r="F42" s="34"/>
+      <c r="F42" s="34">
+        <v>1201528.4000000004</v>
+      </c>
       <c r="G42"/>
       <c r="H42"/>
       <c r="I42"/>
@@ -3599,11 +3604,11 @@
       </c>
       <c r="C67" s="23">
         <f>SUM(C13:C66)</f>
-        <v>234510082.63999999</v>
+        <v>242482347.47999999</v>
       </c>
       <c r="F67" s="23">
         <f>SUM(F13:F66)</f>
-        <v>18645829.339999996</v>
+        <v>19847357.739999995</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
